--- a/assets/2.2_行业周度概览.xlsx
+++ b/assets/2.2_行业周度概览.xlsx
@@ -31,91 +31,91 @@
     <t>行业平均周度换手率占比分位数</t>
   </si>
   <si>
+    <t>轻工制造</t>
+  </si>
+  <si>
+    <t>综合</t>
+  </si>
+  <si>
+    <t>农林牧渔</t>
+  </si>
+  <si>
+    <t>传媒</t>
+  </si>
+  <si>
+    <t>纺织服装</t>
+  </si>
+  <si>
+    <t>房地产</t>
+  </si>
+  <si>
+    <t>石油石化</t>
+  </si>
+  <si>
+    <t>煤炭</t>
+  </si>
+  <si>
+    <t>基础化工</t>
+  </si>
+  <si>
+    <t>商贸零售</t>
+  </si>
+  <si>
+    <t>消费者服务</t>
+  </si>
+  <si>
+    <t>建材</t>
+  </si>
+  <si>
+    <t>有色金属</t>
+  </si>
+  <si>
+    <t>银行</t>
+  </si>
+  <si>
+    <t>电力及公用事业</t>
+  </si>
+  <si>
+    <t>钢铁</t>
+  </si>
+  <si>
+    <t>国防军工</t>
+  </si>
+  <si>
+    <t>电力设备及新能源</t>
+  </si>
+  <si>
     <t>食品饮料</t>
   </si>
   <si>
-    <t>消费者服务</t>
-  </si>
-  <si>
-    <t>农林牧渔</t>
-  </si>
-  <si>
-    <t>综合</t>
-  </si>
-  <si>
-    <t>基础化工</t>
-  </si>
-  <si>
-    <t>建材</t>
-  </si>
-  <si>
-    <t>纺织服装</t>
-  </si>
-  <si>
-    <t>石油石化</t>
-  </si>
-  <si>
-    <t>电力设备及新能源</t>
-  </si>
-  <si>
-    <t>轻工制造</t>
-  </si>
-  <si>
-    <t>电力及公用事业</t>
-  </si>
-  <si>
-    <t>煤炭</t>
-  </si>
-  <si>
-    <t>商贸零售</t>
+    <t>医药</t>
+  </si>
+  <si>
+    <t>交通运输</t>
+  </si>
+  <si>
+    <t>建筑</t>
+  </si>
+  <si>
+    <t>计算机</t>
+  </si>
+  <si>
+    <t>综合金融</t>
+  </si>
+  <si>
+    <t>非银行金融</t>
+  </si>
+  <si>
+    <t>电子</t>
+  </si>
+  <si>
+    <t>通信</t>
   </si>
   <si>
     <t>家电</t>
   </si>
   <si>
-    <t>钢铁</t>
-  </si>
-  <si>
-    <t>交通运输</t>
-  </si>
-  <si>
-    <t>房地产</t>
-  </si>
-  <si>
-    <t>医药</t>
-  </si>
-  <si>
-    <t>有色金属</t>
-  </si>
-  <si>
-    <t>建筑</t>
-  </si>
-  <si>
-    <t>银行</t>
-  </si>
-  <si>
-    <t>综合金融</t>
-  </si>
-  <si>
-    <t>传媒</t>
-  </si>
-  <si>
-    <t>电子</t>
-  </si>
-  <si>
-    <t>国防军工</t>
-  </si>
-  <si>
     <t>汽车</t>
-  </si>
-  <si>
-    <t>非银行金融</t>
-  </si>
-  <si>
-    <t>计算机</t>
-  </si>
-  <si>
-    <t>通信</t>
   </si>
   <si>
     <t>机械</t>
@@ -501,16 +501,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.028863191604614</v>
+        <v>1.402149558067322</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>8.95110370354219</v>
+        <v>10.61208730005804</v>
       </c>
       <c r="E2">
-        <v>29.41176414489746</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -518,16 +518,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.039303302764893</v>
+        <v>0.2992154955863953</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>15.04725722968578</v>
+        <v>10.7452391748843</v>
       </c>
       <c r="E3">
-        <v>35.29411697387695</v>
+        <v>27.77777862548828</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -535,16 +535,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.294694066047668</v>
+        <v>1.523810267448425</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>16.24705991915294</v>
+        <v>12.71509434155055</v>
       </c>
       <c r="E4">
-        <v>76.47058868408203</v>
+        <v>33.33333206176758</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -552,16 +552,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.2739466428756714</v>
+        <v>3.596773386001587</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>16.2332694115846</v>
+        <v>20.10235997779029</v>
       </c>
       <c r="E5">
-        <v>64.70587921142578</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -569,16 +569,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>10.76760101318359</v>
+        <v>1.048809170722961</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>17.29110153286443</v>
+        <v>10.83516108155251</v>
       </c>
       <c r="E6">
-        <v>35.29411697387695</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -586,16 +586,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.03691565990448</v>
+        <v>1.841635584831238</v>
       </c>
       <c r="C7">
         <v>100</v>
       </c>
       <c r="D7">
-        <v>12.94929305244895</v>
+        <v>9.054843370644551</v>
       </c>
       <c r="E7">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -603,16 +603,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.8075078725814819</v>
+        <v>0.8479873538017273</v>
       </c>
       <c r="C8">
-        <v>92.30769348144531</v>
+        <v>92.85713958740234</v>
       </c>
       <c r="D8">
-        <v>19.15473703861237</v>
+        <v>7.365215756729538</v>
       </c>
       <c r="E8">
-        <v>82.35294342041016</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -620,16 +620,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.79928058385849</v>
+        <v>0.8478202819824219</v>
       </c>
       <c r="C9">
-        <v>92.30769348144531</v>
+        <v>92.85713958740234</v>
       </c>
       <c r="D9">
-        <v>12.36038639148076</v>
+        <v>5.000666603446007</v>
       </c>
       <c r="E9">
-        <v>29.41176414489746</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -637,16 +637,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>12.17472648620605</v>
+        <v>10.50706481933594</v>
       </c>
       <c r="C10">
-        <v>92.30769348144531</v>
+        <v>92.85713958740234</v>
       </c>
       <c r="D10">
-        <v>18.29832094758749</v>
+        <v>10.49058476406255</v>
       </c>
       <c r="E10">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -654,16 +654,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.240203142166138</v>
+        <v>1.402745723724365</v>
       </c>
       <c r="C11">
-        <v>84.61538696289062</v>
+        <v>85.71428680419922</v>
       </c>
       <c r="D11">
-        <v>14.78046877432421</v>
+        <v>11.99972529376595</v>
       </c>
       <c r="E11">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -671,16 +671,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>2.790561199188232</v>
+        <v>0.8248766660690308</v>
       </c>
       <c r="C12">
-        <v>84.61538696289062</v>
+        <v>85.71428680419922</v>
       </c>
       <c r="D12">
-        <v>11.88810963726981</v>
+        <v>10.43628042936325</v>
       </c>
       <c r="E12">
-        <v>29.41176414489746</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -688,16 +688,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.7649428248405457</v>
+        <v>0.900839626789093</v>
       </c>
       <c r="C13">
-        <v>76.92308044433594</v>
+        <v>78.57142639160156</v>
       </c>
       <c r="D13">
-        <v>12.53428905540042</v>
+        <v>8.59296000845292</v>
       </c>
       <c r="E13">
-        <v>70.58823394775391</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -705,16 +705,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>1.286736130714417</v>
+        <v>6.442385196685791</v>
       </c>
       <c r="C14">
-        <v>76.92308044433594</v>
+        <v>78.57142639160156</v>
       </c>
       <c r="D14">
-        <v>15.99199806370781</v>
+        <v>9.457967915534972</v>
       </c>
       <c r="E14">
-        <v>52.94117736816406</v>
+        <v>11.11111068725586</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -722,16 +722,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1.455329775810242</v>
+        <v>1.804975986480713</v>
       </c>
       <c r="C15">
-        <v>76.92308044433594</v>
+        <v>78.57142639160156</v>
       </c>
       <c r="D15">
-        <v>10.12292147498755</v>
+        <v>2.20601190058958</v>
       </c>
       <c r="E15">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -739,16 +739,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.878680944442749</v>
+        <v>2.690324306488037</v>
       </c>
       <c r="C16">
-        <v>69.23076629638672</v>
+        <v>78.57142639160156</v>
       </c>
       <c r="D16">
-        <v>7.951126965192648</v>
+        <v>7.204459361243977</v>
       </c>
       <c r="E16">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -756,16 +756,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>1.465265989303589</v>
+        <v>0.8953642249107361</v>
       </c>
       <c r="C17">
-        <v>69.23076629638672</v>
+        <v>71.42857360839844</v>
       </c>
       <c r="D17">
-        <v>7.949739794905593</v>
+        <v>4.574826870973293</v>
       </c>
       <c r="E17">
-        <v>23.52941131591797</v>
+        <v>16.66666603088379</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -773,16 +773,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>1.452008843421936</v>
+        <v>2.737276554107666</v>
       </c>
       <c r="C18">
-        <v>61.53845977783203</v>
+        <v>71.42857360839844</v>
       </c>
       <c r="D18">
-        <v>13.99687361829686</v>
+        <v>14.61145446123171</v>
       </c>
       <c r="E18">
-        <v>35.29411697387695</v>
+        <v>44.44444274902344</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -790,16 +790,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>6.116149425506592</v>
+        <v>9.377656936645508</v>
       </c>
       <c r="C19">
-        <v>61.53845977783203</v>
+        <v>71.42857360839844</v>
       </c>
       <c r="D19">
-        <v>11.08940038997793</v>
+        <v>10.48291935920715</v>
       </c>
       <c r="E19">
-        <v>23.52941131591797</v>
+        <v>16.66666603088379</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -807,16 +807,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>5.961148262023926</v>
+        <v>1.534617066383362</v>
       </c>
       <c r="C20">
-        <v>53.84615325927734</v>
+        <v>64.28571319580078</v>
       </c>
       <c r="D20">
-        <v>16.62882887077332</v>
+        <v>5.716612091118639</v>
       </c>
       <c r="E20">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -824,16 +824,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>1.672940731048584</v>
+        <v>5.49920129776001</v>
       </c>
       <c r="C21">
-        <v>46.15384674072266</v>
+        <v>57.14285659790039</v>
       </c>
       <c r="D21">
-        <v>13.52814692921109</v>
+        <v>7.759313341449289</v>
       </c>
       <c r="E21">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -841,16 +841,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>1.447311997413635</v>
+        <v>1.428879380226135</v>
       </c>
       <c r="C22">
-        <v>46.15384674072266</v>
+        <v>57.14285659790039</v>
       </c>
       <c r="D22">
-        <v>2.988704733195759</v>
+        <v>4.543139032232083</v>
       </c>
       <c r="E22">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -858,16 +858,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>0.1207493469119072</v>
+        <v>1.672070980072021</v>
       </c>
       <c r="C23">
-        <v>38.46154022216797</v>
+        <v>42.85714340209961</v>
       </c>
       <c r="D23">
-        <v>8.405499792098999</v>
+        <v>10.14636729676046</v>
       </c>
       <c r="E23">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -875,16 +875,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>2.506840944290161</v>
+        <v>8.438728332519531</v>
       </c>
       <c r="C24">
-        <v>30.76922988891602</v>
+        <v>35.71428680419922</v>
       </c>
       <c r="D24">
-        <v>17.16931564467294</v>
+        <v>15.47635671761301</v>
       </c>
       <c r="E24">
-        <v>41.17647171020508</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -892,16 +892,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>14.55300426483154</v>
+        <v>0.1185188516974449</v>
       </c>
       <c r="C25">
-        <v>23.07692337036133</v>
+        <v>28.5714282989502</v>
       </c>
       <c r="D25">
-        <v>13.61083087373164</v>
+        <v>5.40672996044159</v>
       </c>
       <c r="E25">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -909,16 +909,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>2.040510892868042</v>
+        <v>2.282447338104248</v>
       </c>
       <c r="C26">
-        <v>23.07692337036133</v>
+        <v>28.5714282989502</v>
       </c>
       <c r="D26">
-        <v>13.47773876761602</v>
+        <v>2.639755090509636</v>
       </c>
       <c r="E26">
-        <v>29.41176414489746</v>
+        <v>11.11111068725586</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -926,16 +926,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>3.628177642822266</v>
+        <v>13.58176898956299</v>
       </c>
       <c r="C27">
-        <v>15.38461494445801</v>
+        <v>21.4285717010498</v>
       </c>
       <c r="D27">
-        <v>10.63210271521816</v>
+        <v>10.72056854059619</v>
       </c>
       <c r="E27">
-        <v>23.52941131591797</v>
+        <v>16.66666603088379</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -943,16 +943,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>2.250099182128906</v>
+        <v>4.566616058349609</v>
       </c>
       <c r="C28">
-        <v>15.38461494445801</v>
+        <v>21.4285717010498</v>
       </c>
       <c r="D28">
-        <v>4.447634769522625</v>
+        <v>14.02184721211757</v>
       </c>
       <c r="E28">
-        <v>17.64705848693848</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -960,16 +960,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>6.413093090057373</v>
+        <v>1.236866235733032</v>
       </c>
       <c r="C29">
-        <v>7.692307472229004</v>
+        <v>14.2857141494751</v>
       </c>
       <c r="D29">
-        <v>17.62588806913959</v>
+        <v>6.629817902332261</v>
       </c>
       <c r="E29">
-        <v>35.29411697387695</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -977,16 +977,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>4.361704349517822</v>
+        <v>3.325907230377197</v>
       </c>
       <c r="C30">
-        <v>7.692307472229004</v>
+        <v>7.142857074737549</v>
       </c>
       <c r="D30">
-        <v>15.0213627017234</v>
+        <v>7.607648421929577</v>
       </c>
       <c r="E30">
-        <v>23.52941131591797</v>
+        <v>11.11111068725586</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -994,16 +994,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>7.349277973175049</v>
+        <v>7.303182125091553</v>
       </c>
       <c r="C31">
-        <v>7.692307472229004</v>
+        <v>7.142857074737549</v>
       </c>
       <c r="D31">
-        <v>13.74900869450707</v>
+        <v>9.56752218509066</v>
       </c>
       <c r="E31">
-        <v>23.52941131591797</v>
+        <v>22.22222137451172</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2.2_行业周度概览.xlsx
+++ b/assets/2.2_行业周度概览.xlsx
@@ -31,94 +31,94 @@
     <t>行业平均周度换手率占比分位数</t>
   </si>
   <si>
+    <t>传媒</t>
+  </si>
+  <si>
+    <t>通信</t>
+  </si>
+  <si>
+    <t>农林牧渔</t>
+  </si>
+  <si>
     <t>轻工制造</t>
   </si>
   <si>
+    <t>计算机</t>
+  </si>
+  <si>
+    <t>纺织服装</t>
+  </si>
+  <si>
+    <t>基础化工</t>
+  </si>
+  <si>
+    <t>国防军工</t>
+  </si>
+  <si>
+    <t>商贸零售</t>
+  </si>
+  <si>
     <t>综合</t>
   </si>
   <si>
-    <t>农林牧渔</t>
-  </si>
-  <si>
-    <t>传媒</t>
-  </si>
-  <si>
-    <t>纺织服装</t>
-  </si>
-  <si>
     <t>房地产</t>
   </si>
   <si>
+    <t>建筑</t>
+  </si>
+  <si>
     <t>石油石化</t>
   </si>
   <si>
+    <t>消费者服务</t>
+  </si>
+  <si>
+    <t>建材</t>
+  </si>
+  <si>
+    <t>银行</t>
+  </si>
+  <si>
+    <t>电力及公用事业</t>
+  </si>
+  <si>
+    <t>医药</t>
+  </si>
+  <si>
+    <t>食品饮料</t>
+  </si>
+  <si>
+    <t>交通运输</t>
+  </si>
+  <si>
+    <t>电子</t>
+  </si>
+  <si>
+    <t>家电</t>
+  </si>
+  <si>
     <t>煤炭</t>
   </si>
   <si>
-    <t>基础化工</t>
-  </si>
-  <si>
-    <t>商贸零售</t>
-  </si>
-  <si>
-    <t>消费者服务</t>
-  </si>
-  <si>
-    <t>建材</t>
-  </si>
-  <si>
     <t>有色金属</t>
   </si>
   <si>
-    <t>银行</t>
-  </si>
-  <si>
-    <t>电力及公用事业</t>
-  </si>
-  <si>
     <t>钢铁</t>
   </si>
   <si>
-    <t>国防军工</t>
-  </si>
-  <si>
     <t>电力设备及新能源</t>
   </si>
   <si>
-    <t>食品饮料</t>
-  </si>
-  <si>
-    <t>医药</t>
-  </si>
-  <si>
-    <t>交通运输</t>
-  </si>
-  <si>
-    <t>建筑</t>
-  </si>
-  <si>
-    <t>计算机</t>
+    <t>机械</t>
   </si>
   <si>
     <t>综合金融</t>
   </si>
   <si>
+    <t>汽车</t>
+  </si>
+  <si>
     <t>非银行金融</t>
-  </si>
-  <si>
-    <t>电子</t>
-  </si>
-  <si>
-    <t>通信</t>
-  </si>
-  <si>
-    <t>家电</t>
-  </si>
-  <si>
-    <t>汽车</t>
-  </si>
-  <si>
-    <t>机械</t>
   </si>
 </sst>
 </file>
@@ -501,16 +501,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.402149558067322</v>
+        <v>5.211001396179199</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
-        <v>10.61208730005804</v>
+        <v>4.662771428695747</v>
       </c>
       <c r="E2">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -518,16 +518,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.2992154955863953</v>
+        <v>7.016651153564453</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>10.7452391748843</v>
+        <v>4.936292584400531</v>
       </c>
       <c r="E3">
-        <v>27.77777862548828</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -535,16 +535,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1.523810267448425</v>
+        <v>1.586331248283386</v>
       </c>
       <c r="C4">
         <v>100</v>
       </c>
       <c r="D4">
-        <v>12.71509434155055</v>
+        <v>3.180358101782345</v>
       </c>
       <c r="E4">
-        <v>33.33333206176758</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -552,16 +552,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>3.596773386001587</v>
+        <v>1.422805190086365</v>
       </c>
       <c r="C5">
         <v>100</v>
       </c>
       <c r="D5">
-        <v>20.10235997779029</v>
+        <v>3.469762439672658</v>
       </c>
       <c r="E5">
-        <v>50</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -569,16 +569,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>1.048809170722961</v>
+        <v>9.684762001037598</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>93.33333587646484</v>
       </c>
       <c r="D6">
-        <v>10.83516108155251</v>
+        <v>4.199124992804395</v>
       </c>
       <c r="E6">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -586,16 +586,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1.841635584831238</v>
+        <v>0.8581921458244324</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>93.33333587646484</v>
       </c>
       <c r="D7">
-        <v>9.054843370644551</v>
+        <v>3.317721988707781</v>
       </c>
       <c r="E7">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -603,16 +603,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.8479873538017273</v>
+        <v>8.081010818481445</v>
       </c>
       <c r="C8">
-        <v>92.85713958740234</v>
+        <v>86.66666412353516</v>
       </c>
       <c r="D8">
-        <v>7.365215756729538</v>
+        <v>3.80117803013853</v>
       </c>
       <c r="E8">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -620,16 +620,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0.8478202819824219</v>
+        <v>3.700535297393799</v>
       </c>
       <c r="C9">
-        <v>92.85713958740234</v>
+        <v>86.66666412353516</v>
       </c>
       <c r="D9">
-        <v>5.000666603446007</v>
+        <v>4.365309897533133</v>
       </c>
       <c r="E9">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -637,16 +637,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>10.50706481933594</v>
+        <v>1.448100686073303</v>
       </c>
       <c r="C10">
-        <v>92.85713958740234</v>
+        <v>86.66666412353516</v>
       </c>
       <c r="D10">
-        <v>10.49058476406255</v>
+        <v>4.244842721131241</v>
       </c>
       <c r="E10">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -654,16 +654,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>1.402745723724365</v>
+        <v>0.2182760685682297</v>
       </c>
       <c r="C11">
-        <v>85.71428680419922</v>
+        <v>80</v>
       </c>
       <c r="D11">
-        <v>11.99972529376595</v>
+        <v>3.410656513079353</v>
       </c>
       <c r="E11">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -671,16 +671,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.8248766660690308</v>
+        <v>1.658030986785889</v>
       </c>
       <c r="C12">
-        <v>85.71428680419922</v>
+        <v>73.33333587646484</v>
       </c>
       <c r="D12">
-        <v>10.43628042936325</v>
+        <v>2.825652836909834</v>
       </c>
       <c r="E12">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -688,16 +688,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.900839626789093</v>
+        <v>1.725985646247864</v>
       </c>
       <c r="C13">
-        <v>78.57142639160156</v>
+        <v>66.66666412353516</v>
       </c>
       <c r="D13">
-        <v>8.59296000845292</v>
+        <v>3.258470987878096</v>
       </c>
       <c r="E13">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -705,16 +705,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>6.442385196685791</v>
+        <v>0.6353676915168762</v>
       </c>
       <c r="C14">
-        <v>78.57142639160156</v>
+        <v>66.66666412353516</v>
       </c>
       <c r="D14">
-        <v>9.457967915534972</v>
+        <v>2.946027440913752</v>
       </c>
       <c r="E14">
-        <v>11.11111068725586</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -722,16 +722,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>1.804975986480713</v>
+        <v>0.7643601894378662</v>
       </c>
       <c r="C15">
-        <v>78.57142639160156</v>
+        <v>66.66666412353516</v>
       </c>
       <c r="D15">
-        <v>2.20601190058958</v>
+        <v>3.618828565414463</v>
       </c>
       <c r="E15">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -739,16 +739,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>2.690324306488037</v>
+        <v>0.8548159003257751</v>
       </c>
       <c r="C16">
-        <v>78.57142639160156</v>
+        <v>66.66666412353516</v>
       </c>
       <c r="D16">
-        <v>7.204459361243977</v>
+        <v>3.378952919910936</v>
       </c>
       <c r="E16">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -756,16 +756,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.8953642249107361</v>
+        <v>1.679705142974854</v>
       </c>
       <c r="C17">
-        <v>71.42857360839844</v>
+        <v>60</v>
       </c>
       <c r="D17">
-        <v>4.574826870973293</v>
+        <v>0.944285715619723</v>
       </c>
       <c r="E17">
-        <v>16.66666603088379</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -773,16 +773,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>2.737276554107666</v>
+        <v>2.197393894195557</v>
       </c>
       <c r="C18">
-        <v>71.42857360839844</v>
+        <v>53.33333206176758</v>
       </c>
       <c r="D18">
-        <v>14.61145446123171</v>
+        <v>2.405510043278011</v>
       </c>
       <c r="E18">
-        <v>44.44444274902344</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -790,16 +790,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>9.377656936645508</v>
+        <v>5.378247261047363</v>
       </c>
       <c r="C19">
-        <v>71.42857360839844</v>
+        <v>46.66666793823242</v>
       </c>
       <c r="D19">
-        <v>10.48291935920715</v>
+        <v>2.379587018193628</v>
       </c>
       <c r="E19">
-        <v>16.66666603088379</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -807,16 +807,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>1.534617066383362</v>
+        <v>1.340023279190063</v>
       </c>
       <c r="C20">
-        <v>64.28571319580078</v>
+        <v>46.66666793823242</v>
       </c>
       <c r="D20">
-        <v>5.716612091118639</v>
+        <v>2.523118204013868</v>
       </c>
       <c r="E20">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -824,16 +824,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>5.49920129776001</v>
+        <v>1.206809639930725</v>
       </c>
       <c r="C21">
-        <v>57.14285659790039</v>
+        <v>40</v>
       </c>
       <c r="D21">
-        <v>7.759313341449289</v>
+        <v>1.697708123340839</v>
       </c>
       <c r="E21">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -841,16 +841,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>1.428879380226135</v>
+        <v>16.09057426452637</v>
       </c>
       <c r="C22">
-        <v>57.14285659790039</v>
+        <v>40</v>
       </c>
       <c r="D22">
-        <v>4.543139032232083</v>
+        <v>4.801807666738187</v>
       </c>
       <c r="E22">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -858,16 +858,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>1.672070980072021</v>
+        <v>1.328221201896667</v>
       </c>
       <c r="C23">
-        <v>42.85714340209961</v>
+        <v>40</v>
       </c>
       <c r="D23">
-        <v>10.14636729676046</v>
+        <v>2.78887261778471</v>
       </c>
       <c r="E23">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -875,16 +875,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>8.438728332519531</v>
+        <v>0.4970538318157196</v>
       </c>
       <c r="C24">
-        <v>35.71428680419922</v>
+        <v>40</v>
       </c>
       <c r="D24">
-        <v>15.47635671761301</v>
+        <v>1.737263882325755</v>
       </c>
       <c r="E24">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -892,16 +892,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>0.1185188516974449</v>
+        <v>4.977017402648926</v>
       </c>
       <c r="C25">
-        <v>28.5714282989502</v>
+        <v>33.33333206176758</v>
       </c>
       <c r="D25">
-        <v>5.40672996044159</v>
+        <v>4.028818407773971</v>
       </c>
       <c r="E25">
-        <v>22.22222137451172</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -909,16 +909,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>2.282447338104248</v>
+        <v>0.6634228825569153</v>
       </c>
       <c r="C26">
-        <v>28.5714282989502</v>
+        <v>33.33333206176758</v>
       </c>
       <c r="D26">
-        <v>2.639755090509636</v>
+        <v>2.15299998739591</v>
       </c>
       <c r="E26">
-        <v>11.11111068725586</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -926,16 +926,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>13.58176898956299</v>
+        <v>7.392091274261475</v>
       </c>
       <c r="C27">
-        <v>21.4285717010498</v>
+        <v>26.66666603088379</v>
       </c>
       <c r="D27">
-        <v>10.72056854059619</v>
+        <v>3.420811241492629</v>
       </c>
       <c r="E27">
-        <v>16.66666603088379</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -943,16 +943,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>4.566616058349609</v>
+        <v>7.30750036239624</v>
       </c>
       <c r="C28">
-        <v>21.4285717010498</v>
+        <v>13.33333301544189</v>
       </c>
       <c r="D28">
-        <v>14.02184721211757</v>
+        <v>3.299607686547266</v>
       </c>
       <c r="E28">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -960,16 +960,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>1.236866235733032</v>
+        <v>0.08599755167961121</v>
       </c>
       <c r="C29">
-        <v>14.2857141494751</v>
+        <v>6.666666507720947</v>
       </c>
       <c r="D29">
-        <v>6.629817902332261</v>
+        <v>1.270210003852844</v>
       </c>
       <c r="E29">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -977,16 +977,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>3.325907230377197</v>
+        <v>3.297961950302124</v>
       </c>
       <c r="C30">
-        <v>7.142857074737549</v>
+        <v>6.666666507720947</v>
       </c>
       <c r="D30">
-        <v>7.607648421929577</v>
+        <v>3.046730707362881</v>
       </c>
       <c r="E30">
-        <v>11.11111068725586</v>
+        <v>10.52631568908691</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -994,16 +994,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>7.303182125091553</v>
+        <v>1.675203204154968</v>
       </c>
       <c r="C31">
-        <v>7.142857074737549</v>
+        <v>6.666666507720947</v>
       </c>
       <c r="D31">
-        <v>9.56752218509066</v>
+        <v>0.864289857717096</v>
       </c>
       <c r="E31">
-        <v>22.22222137451172</v>
+        <v>5.263157844543457</v>
       </c>
     </row>
   </sheetData>
